--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -581,12 +581,12 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-17, 2026-03-18, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-17, 2026-03-18, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -607,22 +607,22 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-23</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-17, 2026-03-23</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
         <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="X2" t="n">
         <v>0.8</v>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -579,21 +579,13 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -605,27 +597,19 @@
           <t>2026-03-03, 2026-03-10, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -669,21 +653,13 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -695,27 +671,19 @@
           <t>2026-03-07, 2026-03-15, 2026-03-18, 2026-03-19, 2026-03-29</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-18, 2026-03-19</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -579,13 +579,21 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -597,19 +605,27 @@
           <t>2026-03-03, 2026-03-10, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
+        </is>
+      </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -653,13 +669,21 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -671,19 +695,27 @@
           <t>2026-03-07, 2026-03-15, 2026-03-18, 2026-03-19, 2026-03-29</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-18, 2026-03-19</t>
+        </is>
+      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -702,20 +702,20 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-18, 2026-03-19</t>
+          <t>2026-03-05, 2026-03-18</t>
         </is>
       </c>
       <c r="U3" t="n">
         <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -607,12 +607,12 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-25</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-25</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -697,25 +697,25 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -607,12 +607,12 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-25</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-25</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -697,12 +697,12 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="U3" t="n">

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,6 +716,718 @@
       </c>
       <c r="X3" t="n">
         <v>0.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>COUNTRY PARK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Nathalia Alvarez Rangel</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vianey Eliana Roa Aceros</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-07, 2026-03-09, 2026-03-11, 2026-03-15, 2026-03-16, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-09, 2026-03-15, 2026-03-16, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SKY TOWER</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Diana Garcia Blanco</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jorge Alberto Sandoval Rodriguez</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-03-09, 2026-03-17, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-03-09, 2026-03-17, 2026-03-24, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PANORAMIK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Diana Garcia Blanco</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tatiana Rondon Villareal</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-12, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-12, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ALCALA GRAN RESERVA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Diana Garcia Blanco</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Maria Ines Castellanos Tarazona</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-17, 2026-03-19, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-19, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PARQUE ORIENTE AURORA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Claudia Patricia Cruz</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>German Alirio Villarreal Solano</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PARQUE ORIENTE SOLEIL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Claudia Patricia Cruz</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Luisa Fernanda Henao Gomez</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11, 2026-03-20, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TERRAZA DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Claudia Patricia Cruz</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Carlos Andres Moreno Villamizar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-13, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-13</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-13, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-13</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BOSQUES DEL HATO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Claudia Patricia Cruz</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fabio Elberto Rodriguez Rodriguez</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-03-09, 2026-03-16, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-11, 2026-03-20, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2026-03-09, 2026-03-16, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-11, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X11"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,7 +1015,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
+          <t>MARTES</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1027,14 +1027,14 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
       <c r="O7" t="n">
         <v>4</v>
       </c>
@@ -1051,20 +1051,24 @@
           <t>2026-03-04, 2026-03-17, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>2026-03-04, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V7" t="n">
         <v>3</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
         <v>0.75</v>
@@ -1428,6 +1432,80 @@
       </c>
       <c r="X11" t="n">
         <v>0.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PARQUE ORIENTE MONTEVISTA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Claudia Patricia Cruz</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Paula Pinto Marin</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -845,7 +845,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -856,7 +856,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -880,18 +880,22 @@
           <t>2026-03-19, 2026-03-26</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
       <c r="U5" t="n">
         <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
@@ -1491,18 +1495,30 @@
       <c r="P12" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-11, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-16, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,122 +429,122 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Gerente</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Director de obra</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ValidacionParametrización</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Cluster</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>HorarioIntermedia</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>HorarioSemanal</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ConteoIntermedia</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ConteoSemanal</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>RealIntermedia</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RealSemanal</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>CoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>CoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>CumplimientoIntermedia</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>CumplimientoSemanal</t>
         </is>
@@ -569,7 +581,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LUNES</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -581,7 +581,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>LUNES</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,122 +417,122 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Gerente</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Director de obra</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ValidacionParametrización</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Cluster</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>HorarioIntermedia</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>HorarioSemanal</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ConteoIntermedia</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ConteoSemanal</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>RealIntermedia</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>RealSemanal</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>CoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>CoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>CumplimientoIntermedia</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>CumplimientoSemanal</t>
         </is>
@@ -609,35 +597,35 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-18, 2026-03-24</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-18, 2026-03-24</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-25</t>
         </is>
       </c>
       <c r="U2" t="n">
         <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="3">
@@ -699,7 +687,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-07, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-07, 2026-03-15, 2026-03-18, 2026-03-19, 2026-03-29</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -709,7 +697,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -718,13 +706,13 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="X3" t="n">
         <v>0.25</v>
@@ -789,7 +777,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-07, 2026-03-09, 2026-03-11, 2026-03-15, 2026-03-16, 2026-03-18, 2026-03-24, 2026-03-25</t>
+          <t>2026-03-07, 2026-03-09, 2026-03-15, 2026-03-16, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -799,7 +787,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -808,13 +796,13 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="X4" t="n">
         <v>0.25</v>
@@ -879,7 +867,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-17, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-09, 2026-03-17, 2026-03-24, 2026-03-26</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -889,7 +877,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-03-19, 2026-03-26</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -898,13 +886,13 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="X5" t="n">
         <v>0.25</v>
@@ -969,7 +957,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-12, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -979,7 +967,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-12, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1059,35 +1047,35 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-17, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-17, 2026-03-19, 2026-03-25</t>
+          <t>2026-03-04, 2026-03-17, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-17, 2026-03-25</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-19, 2026-03-25</t>
+          <t>2026-03-04, 2026-03-25</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X7" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -1149,35 +1137,35 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>2026-03-06, 2026-03-11, 2026-03-18, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="U8" t="n">
         <v>4</v>
       </c>
       <c r="V8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9">
@@ -1239,22 +1227,22 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-12, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-12, 2026-03-26</t>
         </is>
       </c>
       <c r="U9" t="n">
@@ -1419,7 +1407,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-11, 2026-03-20, 2026-03-25</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1429,7 +1417,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-11, 2026-03-25</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1509,7 +1497,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-16, 2026-03-27</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1517,20 +1505,16 @@
           <t>2026-03-06, 2026-03-16, 2026-03-27</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-18, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-24</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -616,13 +616,13 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
         <v>3</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X2" t="n">
         <v>0.75</v>
@@ -967,25 +967,25 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-12, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-12, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7">
@@ -1237,25 +1237,25 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-11</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-12, 2026-03-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10">
@@ -1327,25 +1327,25 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-13, 2026-03-25</t>
+          <t>2026-03-04, 2026-03-25</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-13</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11">
@@ -1417,25 +1417,25 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-11, 2026-03-25</t>
+          <t>2026-03-03, 2026-03-25</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-11, 2026-03-25</t>
+          <t>2026-03-03, 2026-03-25</t>
         </is>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
